--- a/Supplementary_Data_5.xlsx
+++ b/Supplementary_Data_5.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1_Raw_dPCR_Data" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2_Mut_Quantification" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3_WT_Quantification" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4_LoB_LoD_LoQ" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5_Ratio_Comparison" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6_R2_R3_Consistency" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7_Threshold_Ranges" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8_Estimates_Summary" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9_MC_CV_Comparison" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_MC_CI_Coverage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="1_Raw_dPCR_Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="2_Mut_Quantification" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="3_WT_Quantification" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="4_LoB_LoD_LoQ" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="5_Ratio_Comparison" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="6_R2_R3_Consistency" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="7_Threshold_Ranges" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="8_Estimates_Summary" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="9_MC_CV_Comparison" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_MC_CI_Coverage" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_KRAS_Stool" sheetId="11" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -690,13 +691,13 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>0.95112</v>
+        <v>0.8575</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8575</v>
+        <v>0.9847399999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>0.85436</v>
+        <v>0.84316</v>
       </c>
       <c r="E3" t="n">
         <v>0.95</v>
@@ -707,10 +708,10 @@
         <v>5</v>
       </c>
       <c r="B4" t="n">
-        <v>0.95222</v>
+        <v>0.8353</v>
       </c>
       <c r="C4" t="n">
-        <v>0.95626</v>
+        <v>0.98188</v>
       </c>
       <c r="D4" t="n">
         <v>0.94442</v>
@@ -724,13 +725,13 @@
         <v>10</v>
       </c>
       <c r="B5" t="n">
-        <v>0.95338</v>
+        <v>0.8838</v>
       </c>
       <c r="C5" t="n">
-        <v>0.95424</v>
+        <v>0.9728</v>
       </c>
       <c r="D5" t="n">
-        <v>0.8838</v>
+        <v>0.94146</v>
       </c>
       <c r="E5" t="n">
         <v>0.95</v>
@@ -741,13 +742,13 @@
         <v>25</v>
       </c>
       <c r="B6" t="n">
-        <v>0.95326</v>
+        <v>0.92396</v>
       </c>
       <c r="C6" t="n">
-        <v>0.94562</v>
+        <v>0.96366</v>
       </c>
       <c r="D6" t="n">
-        <v>0.94562</v>
+        <v>0.9352200000000001</v>
       </c>
       <c r="E6" t="n">
         <v>0.95</v>
@@ -758,13 +759,13 @@
         <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>0.94696</v>
+        <v>0.9353</v>
       </c>
       <c r="C7" t="n">
-        <v>0.95726</v>
+        <v>0.9567</v>
       </c>
       <c r="D7" t="n">
-        <v>0.95224</v>
+        <v>0.94534</v>
       </c>
       <c r="E7" t="n">
         <v>0.95</v>
@@ -775,13 +776,13 @@
         <v>100</v>
       </c>
       <c r="B8" t="n">
-        <v>0.952</v>
+        <v>0.94378</v>
       </c>
       <c r="C8" t="n">
-        <v>0.94962</v>
+        <v>0.95802</v>
       </c>
       <c r="D8" t="n">
-        <v>0.94962</v>
+        <v>0.9436</v>
       </c>
       <c r="E8" t="n">
         <v>0.95</v>
@@ -792,10 +793,10 @@
         <v>500</v>
       </c>
       <c r="B9" t="n">
-        <v>0.94806</v>
+        <v>0.95098</v>
       </c>
       <c r="C9" t="n">
-        <v>0.95448</v>
+        <v>0.9513200000000001</v>
       </c>
       <c r="D9" t="n">
         <v>0.9513200000000001</v>
@@ -809,13 +810,13 @@
         <v>1000</v>
       </c>
       <c r="B10" t="n">
-        <v>0.95058</v>
+        <v>0.95046</v>
       </c>
       <c r="C10" t="n">
-        <v>0.95046</v>
+        <v>0.9527600000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>0.95046</v>
+        <v>0.9503200000000001</v>
       </c>
       <c r="E10" t="n">
         <v>0.95</v>
@@ -826,16 +827,286 @@
         <v>5000</v>
       </c>
       <c r="B11" t="n">
-        <v>0.94878</v>
+        <v>0.9499</v>
       </c>
       <c r="C11" t="n">
-        <v>0.95084</v>
+        <v>0.9496</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9499</v>
+        <v>0.9496</v>
       </c>
       <c r="E11" t="n">
         <v>0.95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>KRAS stool DNA assay: aggregate published counts and TCS reanalysis</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>Source: Vogelstein and Kinzler (1999); per-well observations were not reported.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Quantity</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Definition / method</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>N_stool_wells</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>288</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Stool-sample wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>k_PCR_positive</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PCR-positive stool wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>k_mutant_positive</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Mutant-positive stool wells</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>raw_mutant_among_PCR_positive</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.04901960784313725</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>5/102 = 4.90%; raw positive-well ratio, not Poisson-corrected abundance</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>M_total_hat_molecules</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>125.9175762497505</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>-288 ln(1 - 102/288)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>M_mutant_hat_molecules</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>5.043911757900006</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-288 ln(1 - 5/288)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>mutant_abundance_hat</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.04005724941763243</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>M_mutant_hat / M_total_hat</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>mutant_abundance_CI95_low</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0.01298361107402252</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CP interval for 5/288, Poisson-transformed; M_total held at its point estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>mutant_abundance_CI95_up</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.0934823289448363</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CP interval for 5/288, Poisson-transformed; M_total held at its point estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>CV_total</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>0.09980527650247183</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Delta-method counting CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CV_mutant</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.4472193110154454</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Delta-method counting CV</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>LoB_molecules</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3.688879454113942</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>One-sided 95% blank bound, Poisson-transformed</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>LoD_molecules</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2.995732273553991</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>R2/R3: -ln(0.05) at n=N</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>LoQ_low_R2_molecules</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>26.17110167115415</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Exact counting CV = 20%</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>LoQ_low_R3_molecules</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>25</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Low-occupancy approximation: 25N/n = 25</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -937,9 +1208,6 @@
       <c r="E3" t="n">
         <v>1.599964605248606e-07</v>
       </c>
-      <c r="F3" t="n">
-        <v/>
-      </c>
       <c r="G3" t="n">
         <v>1.599964605248606e-07</v>
       </c>
@@ -1140,7 +1408,7 @@
         <v>5811.28191337156</v>
       </c>
       <c r="J8" t="n">
-        <v>6196.082964987344</v>
+        <v>6196.082964987361</v>
       </c>
       <c r="K8" t="n">
         <v>5811.831692969012</v>
@@ -1956,10 +2224,6 @@
           <t>Note: R2 exact and R3 linear approximation yield identical LoD in the dPCR limit.</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1967,10 +2231,6 @@
           <t>This confirms the dPCR-R3 reduction as the κ→0 limit of the full TCS master equation.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2422,10 +2682,10 @@
         <v>55.30822300612662</v>
       </c>
       <c r="D4" t="n">
-        <v>55.15284569885045</v>
+        <v>55.15284569885046</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9971907015117993</v>
+        <v>0.9971907015117996</v>
       </c>
     </row>
     <row r="5">
@@ -2459,7 +2719,7 @@
         <v>24.72631876982962</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9996343905768201</v>
+        <v>0.9996343905768202</v>
       </c>
     </row>
     <row r="7">
@@ -2507,7 +2767,7 @@
         <v>5.535102826703867</v>
       </c>
       <c r="D9" t="n">
-        <v>5.539916063948165</v>
+        <v>5.539916063948164</v>
       </c>
       <c r="E9" t="n">
         <v>1.000869584070069</v>
